--- a/testbuild/CodeSystem-vkp-cfs-score.codesystem.xlsx
+++ b/testbuild/CodeSystem-vkp-cfs-score.codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T09:03:30+00:00</t>
+    <t>2026-10-02T10:19:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/testbuild/CodeSystem-vkp-cfs-score.codesystem.xlsx
+++ b/testbuild/CodeSystem-vkp-cfs-score.codesystem.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T10:19:39+00:00</t>
+    <t>2026-10-02T10:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
